--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39714.76</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24737.57</v>
+        <v>24602.36</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28758.98</v>
+        <v>28892.92</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39714.76</v>
+        <v>39995.05</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>78845.03999999999</v>
+        <v>79202.33</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44619.31</v>
+        <v>44676.51</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65077.46</v>
+        <v>65433.35</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38780.92</v>
+        <v>38781.17</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>40858.43</v>
+        <v>42097.39</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>60428.51</v>
+        <v>59976.26</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>28492.26</v>
+        <v>28372.13</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>39694.17</v>
+        <v>40847.14</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22290.84</v>
+        <v>22194.81</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38100.59</v>
+        <v>37349.19</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>42659.19</v>
+        <v>43144.32</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30293.61</v>
+        <v>30519.29</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38968.76</v>
+        <v>38673.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27437.64</v>
+        <v>26974.06</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>49632.37</v>
+        <v>50371.41</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28194.2</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>31943.13</v>
+        <v>31571.45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1095-90-CM25</t>
+          <t>2332-142-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39510.7</v>
+        <v>25559.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4132-252-CM25</t>
+          <t>946-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>24602.36</v>
+        <v>35519.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4180-171-CM25</t>
+          <t>1426102-106-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28892.92</v>
+        <v>29003.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4090-386-CM25</t>
+          <t>1095-90-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39995.05</v>
+        <v>39510.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3289-226-CM25</t>
+          <t>4132-252-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42056.86</v>
+        <v>24602.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2289-1106-CM25</t>
+          <t>4180-171-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>79202.33</v>
+        <v>28892.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2324-1974-CM25</t>
+          <t>4090-386-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44676.51</v>
+        <v>39995.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2324-2018-CM25</t>
+          <t>3289-226-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65433.35</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3888-16-CM26</t>
+          <t>2289-1106-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38781.17</v>
+        <v>79202.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2289-112-CM26</t>
+          <t>2324-1974-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>42097.39</v>
+        <v>44676.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2660-11-CM26</t>
+          <t>2324-2018-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>59976.26</v>
+        <v>65433.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>656-36-CM26</t>
+          <t>3888-16-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>28372.13</v>
+        <v>38781.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2289-293-CM26</t>
+          <t>2289-112-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>40847.14</v>
+        <v>42097.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5413-210-CM26</t>
+          <t>2660-11-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22194.81</v>
+        <v>59976.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4090-97-CM26</t>
+          <t>656-36-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>37349.19</v>
+        <v>28372.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5413-342-CM26</t>
+          <t>2289-293-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>43144.32</v>
+        <v>40847.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4037-248-CM26</t>
+          <t>5413-210-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.220.400-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRESIA</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30519.29</v>
+        <v>22194.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4042-123-CM26</t>
+          <t>4090-97-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>Automotriz Tecnosur Limitada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38673.14</v>
+        <v>37349.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4195-680-CM26</t>
+          <t>5413-342-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>26974.06</v>
+        <v>43144.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3723-58-CM26</t>
+          <t>4037-248-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.400-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>50371.41</v>
+        <v>30519.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>4042-123-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Ilustre Municipalidad de Fresia - Salud</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>28388.86</v>
+        <v>38673.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2885-339-CM26</t>
+          <t>4195-680-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,6 +1850,189 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>26974.06</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3723-58-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.230.800-k</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>50371.41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1269-43-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>28388.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2885-339-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.210.600-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>31571.45</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2332-142-CM25</t>
+          <t>2289-14-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25559.93</v>
+        <v>32413.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>946-1-CM25</t>
+          <t>2332-142-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35519.88</v>
+        <v>25559.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1426102-106-CM25</t>
+          <t>2660-20-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Comercial Motores de los Andes SpA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29003.03</v>
+        <v>19839.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1095-90-CM25</t>
+          <t>1037-30-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39510.7</v>
+        <v>36986.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4132-252-CM25</t>
+          <t>946-1-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>24602.36</v>
+        <v>35519.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4180-171-CM25</t>
+          <t>1426102-78-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28892.92</v>
+        <v>27447.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4090-386-CM25</t>
+          <t>2324-512-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39995.05</v>
+        <v>41129.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3289-226-CM25</t>
+          <t>1095-21-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42056.86</v>
+        <v>35180.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2289-1106-CM25</t>
+          <t>1095-22-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SKC Transportes S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.176.602-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>79202.33</v>
+        <v>125218.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2324-1974-CM25</t>
+          <t>1426102-106-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>44676.51</v>
+        <v>29003.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2324-2018-CM25</t>
+          <t>2289-573-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>65433.35</v>
+        <v>71932.64999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3888-16-CM26</t>
+          <t>2297-802-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,28 +1225,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38781.17</v>
+        <v>78539.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2289-112-CM26</t>
+          <t>5413-512-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1260,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1275,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42097.39</v>
+        <v>33776.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2660-11-CM26</t>
+          <t>2289-622-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>59976.26</v>
+        <v>25085.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>656-36-CM26</t>
+          <t>4318-23-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1382,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>69.230.500-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28372.13</v>
+        <v>21630.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2289-293-CM26</t>
+          <t>2904-606-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.252.200-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE HUALAIHUE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>40847.14</v>
+        <v>32712.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5413-210-CM26</t>
+          <t>3479-1107-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1504,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,28 +1549,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>22194.81</v>
+        <v>34813.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4090-97-CM26</t>
+          <t>2989-467-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1610,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>37349.19</v>
+        <v>30631.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5413-342-CM26</t>
+          <t>1388974-145-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>71.146.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,43 +1671,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>43144.32</v>
+        <v>34130.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4037-248-CM26</t>
+          <t>2297-1138-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.220.400-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRESIA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1732,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>30519.29</v>
+        <v>10637.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4042-123-CM26</t>
+          <t>2852-754-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1789,28 +1793,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>38673.14</v>
+        <v>22045.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4195-680-CM26</t>
+          <t>2324-1259-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1854,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26974.06</v>
+        <v>18523.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3723-58-CM26</t>
+          <t>3888-456-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,28 +1915,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>50371.41</v>
+        <v>37855.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>1002-409-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1957,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,28 +1976,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>28388.86</v>
+        <v>34923.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2885-339-CM26</t>
+          <t>3723-219-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2037,1601 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
+        <v>72327.34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1002-453-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>154173.32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1002-452-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>149680.45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4180-159-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>POMPEYO CARRASCO SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>23337.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1095-90-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>39510.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4132-252-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>24602.36</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4180-171-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>28892.92</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4090-386-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.220.500-6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>39995.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3289-226-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>42056.86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2289-1106-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>79202.33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2324-1974-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>44676.51</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2324-2018-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>65433.35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3888-16-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>38781.17</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2289-112-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>42097.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2660-11-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.230.100-5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>59976.26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>656-36-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.818.001-8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>28372.13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2289-293-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>40847.14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5413-210-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>22194.81</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4090-97-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.220.500-6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Automotriz Tecnosur Limitada</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>37349.19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5413-342-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>43144.32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4037-248-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.220.400-K</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>30519.29</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4042-123-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.220.402-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Fresia - Salud</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>38673.14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4195-680-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.230.200-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>26974.06</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3723-58-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.230.800-k</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>50371.41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1269-43-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>28388.86</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2885-339-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.210.600-8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
         <v>31571.45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2324-1056-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>44713.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2043,7 +2043,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1002-453-CM25</t>
+          <t>1002-452-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>154173.32</v>
+        <v>149680.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1002-452-CM25</t>
+          <t>1002-453-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>149680.45</v>
+        <v>154173.32</v>
       </c>
     </row>
     <row r="29">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4090-386-CM25</t>
+          <t>1347776-13-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>39995.05</v>
+        <v>61220.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3289-226-CM25</t>
+          <t>4090-386-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>42056.86</v>
+        <v>39995.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2289-1106-CM25</t>
+          <t>3289-226-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>79202.33</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2324-1974-CM25</t>
+          <t>2289-1106-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2615,22 +2615,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>44676.51</v>
+        <v>79202.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2324-2018-CM25</t>
+          <t>2324-1974-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>65433.35</v>
+        <v>44676.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3888-16-CM26</t>
+          <t>2324-2018-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2732,27 +2732,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>38781.17</v>
+        <v>65433.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2289-112-CM26</t>
+          <t>3888-16-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>42097.39</v>
+        <v>38781.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2660-11-CM26</t>
+          <t>1350104-5-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>65.084.447-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>ASOCIACIÓN DE MUNICIPALIDADES DE LA PROVINCIA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>59976.26</v>
+        <v>21954.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>656-36-CM26</t>
+          <t>2289-112-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2915,27 +2915,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.818.001-8</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>28372.13</v>
+        <v>42097.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2289-293-CM26</t>
+          <t>2660-11-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>40847.14</v>
+        <v>59976.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5413-210-CM26</t>
+          <t>656-36-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.818.001-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION X REGION</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,43 +3082,43 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>22194.81</v>
+        <v>28372.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4090-97-CM26</t>
+          <t>2289-293-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,43 +3143,43 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>37349.19</v>
+        <v>40847.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5413-342-CM26</t>
+          <t>1456840-10-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3204,28 +3204,28 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>43144.32</v>
+        <v>24347.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4037-248-CM26</t>
+          <t>5413-210-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.220.400-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRESIA</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3265,43 +3265,43 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>30519.29</v>
+        <v>22194.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4042-123-CM26</t>
+          <t>4090-97-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>38673.14</v>
+        <v>37349.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4195-680-CM26</t>
+          <t>5413-342-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3342,27 +3342,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.230.200-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUEMCHI</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>26974.06</v>
+        <v>43144.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3723-58-CM26</t>
+          <t>4037-248-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3403,27 +3403,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.400-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3448,13 +3448,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>50371.41</v>
+        <v>30519.29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1269-43-CM26</t>
+          <t>4042-123-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>28388.86</v>
+        <v>38673.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2885-339-CM26</t>
+          <t>4195-680-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3525,27 +3525,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.230.200-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE QUEMCHI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>31571.45</v>
+        <v>26974.06</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2324-1056-CM26</t>
+          <t>3723-58-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3631,7 +3631,312 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
+        <v>50371.41</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1269-43-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>28388.86</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2885-339-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.210.600-8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>31571.45</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2324-1056-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
         <v>44713.44</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5413-979-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>32671.57</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2885-435-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.210.600-8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>17016.13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1338,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1403,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1468,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1533,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1598,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1663,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1728,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1793,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1858,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1923,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1988,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2053,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2118,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2313,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2282,7 +2378,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2443,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2508,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2573,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2638,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2703,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2768,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2709,7 +2833,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2770,7 +2898,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2831,7 +2963,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2892,7 +3028,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2953,7 +3093,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3014,7 +3158,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3075,7 +3223,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3136,7 +3288,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3197,7 +3353,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3258,7 +3418,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3380,7 +3544,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3441,7 +3609,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3502,7 +3674,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3624,7 +3800,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3685,7 +3865,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3746,7 +3930,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3807,7 +3995,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3868,7 +4060,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3929,7 +4125,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -4012,7 +4012,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5413-979-CM26</t>
+          <t>2885-435-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4071,13 +4071,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>32671.57</v>
+        <v>17016.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2885-435-CM26</t>
+          <t>2852-1097-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4117,17 +4117,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>17016.13</v>
+        <v>52477.06</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/los-lagos.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
